--- a/artfynd/A 27444-2023 artfynd.xlsx
+++ b/artfynd/A 27444-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,8 +793,16 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98344685</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27444-2023 artfynd.xlsx
+++ b/artfynd/A 27444-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,9 +799,261 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135707438</v>
+      </c>
+      <c r="B3" t="n">
+        <v>110242</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Västermossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>424195</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6498319</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mariestad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lugnås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Innerslänt</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gabriella Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anna Bergqvist, Gabriella Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135707438</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135707439</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106318</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västermossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>424230</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6498326</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mariestad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lugnås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Flera delar av VO</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gabriella Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna Bergqvist, Gabriella Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135707439</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27444-2023 artfynd.xlsx
+++ b/artfynd/A 27444-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,9 +799,261 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135707438</v>
+      </c>
+      <c r="B3" t="n">
+        <v>110247</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Västermossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>424195</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6498319</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mariestad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lugnås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Innerslänt</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gabriella Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anna Bergqvist, Gabriella Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135707438</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135707439</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106323</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västermossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>424230</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6498326</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mariestad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lugnås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Flera delar av VO</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gabriella Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna Bergqvist, Gabriella Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135707439</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27444-2023 artfynd.xlsx
+++ b/artfynd/A 27444-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135707438</v>
       </c>
       <c r="B3" t="n">
-        <v>110247</v>
+        <v>110249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>135707439</v>
       </c>
       <c r="B4" t="n">
-        <v>106323</v>
+        <v>106325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
